--- a/task135/golden/growth_share_2027.xlsx
+++ b/task135/golden/growth_share_2027.xlsx
@@ -42,7 +42,7 @@
     <t>Expected volatility, daily returns with one-day lead and lag (%)</t>
   </si>
   <si>
-    <t>Expected volatility, weekly returns, Friday to Friday (%)</t>
+    <t>Expected volatility, daily returns, lagged covariances to five days (%)</t>
   </si>
   <si>
     <t>Inside the cap</t>
@@ -69,10 +69,10 @@
     <t>1. Expected volatility is the standard deviation of the portfolio's twelve-month total return (investment policy 4.1 to 4.4), estimated from the six holdings' total returns over the two years to the 30 November 2026 valuation, combined at each growth share's policy weights.</t>
   </si>
   <si>
-    <t>2. The Kestwick funds are dealt at their 12 noon valuation point from each market's latest prices, so the North American fund's price on a day carries the previous evening's New York close; the Fernside shares are priced at the London close. The mandate's daily return correlates 0.20 with the North American fund's on the same day and 0.49 with the fund's next-day return, so co-movement is measured where the prices line up: the daily covariances with the one-day lead and lag added, and weekly returns.</t>
-  </si>
-  <si>
-    <t>3. At 70 per cent growth both estimates are over the cap (11.0 and 10.3 per cent). The daily covariance on its own, scaled by the square root of 252, gives 9.4 per cent at 70 per cent, because it misses the co-movement that lands a day apart.</t>
+    <t>2. The Kestwick funds are dealt at their 12 noon valuation point from each market's latest prices, so the North American fund's price on a day carries the previous evening's New York close; the Fernside shares are priced at the London close. The mandate's daily return correlates 0.20 with the North American fund's on the same day and 0.49 with the fund's next-day return, so the twelve-month variance takes in the co-movement that lands a day apart: the daily covariances with the one-day lead and lag added, and, as a check, the daily covariances lagged out to five days.</t>
+  </si>
+  <si>
+    <t>3. At 70 per cent growth both estimates are over the cap (11.0 and 10.6 per cent). The daily covariance on its own, scaled by the square root of 252, gives 9.4 per cent at 70 per cent, because it misses the co-movement that lands a day apart.</t>
   </si>
   <si>
     <t>4. Investment income (finance procedure 7.2 and 7.3): the mandate's dividends with ex-dividend dates from 1 December 2025 to 30 November 2026, one amount per designation, security and event (the custodian's income report repeats each holding's entitlement on every tax lot line), over the mandate's market value at 30 November with its cash and without accrued income; each Kestwick fund's distributions per income unit over the same twelve months, over its 30 November price. Each yield is applied to the share the step's policy weights give the holding of the portfolio's market value, GBP 32,908,401.</t>
@@ -581,7 +581,7 @@
         <v>5.2</v>
       </c>
       <c r="C10" s="7">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="D10" s="8" t="s">
         <v>12</v>
@@ -602,7 +602,7 @@
         <v>6</v>
       </c>
       <c r="C11" s="7">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>12</v>
@@ -623,7 +623,7 @@
         <v>7</v>
       </c>
       <c r="C12" s="7">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="D12" s="8" t="s">
         <v>12</v>
@@ -644,7 +644,7 @@
         <v>8.3</v>
       </c>
       <c r="C13" s="7">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>12</v>
@@ -665,7 +665,7 @@
         <v>9.6</v>
       </c>
       <c r="C14" s="10">
-        <v>9</v>
+        <v>9.3</v>
       </c>
       <c r="D14" s="11" t="s">
         <v>12</v>
@@ -686,7 +686,7 @@
         <v>11</v>
       </c>
       <c r="C15" s="7">
-        <v>10.3</v>
+        <v>10.6</v>
       </c>
       <c r="D15" s="8" t="s">
         <v>13</v>
@@ -707,7 +707,7 @@
         <v>12.4</v>
       </c>
       <c r="C16" s="7">
-        <v>11.8</v>
+        <v>12.1</v>
       </c>
       <c r="D16" s="8" t="s">
         <v>13</v>
@@ -728,7 +728,7 @@
         <v>13.9</v>
       </c>
       <c r="C17" s="7">
-        <v>13.2</v>
+        <v>13.5</v>
       </c>
       <c r="D17" s="8" t="s">
         <v>13</v>
@@ -749,7 +749,7 @@
         <v>15.4</v>
       </c>
       <c r="C18" s="7">
-        <v>14.7</v>
+        <v>14.9</v>
       </c>
       <c r="D18" s="8" t="s">
         <v>13</v>
